--- a/data/trans_dic/P2C_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
+          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,29; 23,82</t>
+          <t>17,64; 23,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,35; 31,4</t>
+          <t>24,28; 31,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,12; 31,24</t>
+          <t>23,45; 31,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,87; 11,69</t>
+          <t>6,94; 11,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,35; 31,37</t>
+          <t>25,79; 31,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,98; 39,91</t>
+          <t>34,04; 39,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,13; 31,56</t>
+          <t>25,05; 31,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,06; 12,45</t>
+          <t>9,27; 12,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,33; 27,18</t>
+          <t>23,25; 27,4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31,09; 35,72</t>
+          <t>31,08; 35,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,36; 30,5</t>
+          <t>25,57; 30,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,63; 11,39</t>
+          <t>8,61; 11,4</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,16; 48,75</t>
+          <t>42,16; 48,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55,01; 61,3</t>
+          <t>55,27; 61,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46,31; 52,17</t>
+          <t>45,74; 51,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 9,16</t>
+          <t>5,3; 9,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>56,2; 62,24</t>
+          <t>56,22; 62,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,26; 81,14</t>
+          <t>75,99; 80,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,91; 63,6</t>
+          <t>57,94; 63,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,4; 42,88</t>
+          <t>12,5; 40,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,29; 54,89</t>
+          <t>50,6; 54,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66,26; 70,47</t>
+          <t>66,43; 70,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53,31; 57,4</t>
+          <t>53,04; 57,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,74; 28,2</t>
+          <t>9,64; 28,43</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42,47; 54,22</t>
+          <t>41,72; 54,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,98; 75,07</t>
+          <t>63,0; 75,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49,67; 62,21</t>
+          <t>50,05; 62,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,21; 9,85</t>
+          <t>5,24; 9,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54,45; 65,76</t>
+          <t>54,35; 65,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,04; 88,79</t>
+          <t>78,58; 88,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,43; 76,2</t>
+          <t>65,62; 76,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,15; 12,21</t>
+          <t>8,35; 12,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49,64; 58,06</t>
+          <t>50,04; 57,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72,89; 80,89</t>
+          <t>72,92; 80,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59,76; 68,58</t>
+          <t>60,21; 68,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,28; 10,36</t>
+          <t>7,13; 10,26</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,72; 39,18</t>
+          <t>34,87; 39,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,13; 51,41</t>
+          <t>47,04; 51,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,9; 46,24</t>
+          <t>41,67; 46,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,13; 8,93</t>
+          <t>5,93; 8,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,93; 47,96</t>
+          <t>44,12; 48,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,66; 63,59</t>
+          <t>59,69; 63,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,13; 53,34</t>
+          <t>49,06; 53,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,62; 32,97</t>
+          <t>11,65; 32,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40,34; 43,43</t>
+          <t>40,34; 43,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54,53; 57,59</t>
+          <t>54,57; 57,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46,42; 49,64</t>
+          <t>46,44; 49,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,54; 21,83</t>
+          <t>9,45; 21,89</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
+          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>117236; 161512</t>
+          <t>119603; 162147</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>174575; 225111</t>
+          <t>174118; 224416</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>119805; 161919</t>
+          <t>121511; 163452</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35355; 60217</t>
+          <t>35711; 59525</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>253500; 313708</t>
+          <t>257945; 312237</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>361013; 423981</t>
+          <t>361559; 424244</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>197418; 247952</t>
+          <t>196765; 247788</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>68419; 94024</t>
+          <t>70035; 94845</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>391569; 456106</t>
+          <t>390126; 459794</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>553251; 635527</t>
+          <t>553089; 636153</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>330668; 397722</t>
+          <t>333325; 400996</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>109612; 144725</t>
+          <t>109436; 144843</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>396380; 458317</t>
+          <t>396364; 458834</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>637106; 709917</t>
+          <t>640079; 707484</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>510333; 574902</t>
+          <t>503990; 572281</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>123129; 209683</t>
+          <t>121446; 209820</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>568276; 629299</t>
+          <t>568428; 632516</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>902090; 959797</t>
+          <t>898844; 957522</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>713802; 783953</t>
+          <t>714198; 787049</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>277409; 959667</t>
+          <t>279658; 909568</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>981377; 1071118</t>
+          <t>987361; 1070882</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1551100; 1649712</t>
+          <t>1555089; 1648094</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1244599; 1339902</t>
+          <t>1238267; 1340667</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>440886; 1276954</t>
+          <t>436733; 1287495</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>123962; 158280</t>
+          <t>121774; 157984</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>163473; 194866</t>
+          <t>163540; 194812</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>133288; 166926</t>
+          <t>134299; 167537</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33686; 63715</t>
+          <t>33884; 63543</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>157999; 190820</t>
+          <t>157695; 190819</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>212235; 238435</t>
+          <t>211000; 238499</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>204423; 238076</t>
+          <t>205020; 238355</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>53808; 80652</t>
+          <t>55179; 80709</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>288939; 337979</t>
+          <t>291273; 337450</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>384913; 427184</t>
+          <t>385097; 427014</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>347084; 398271</t>
+          <t>349653; 397831</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>95157; 135375</t>
+          <t>93172; 134055</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>663183; 748468</t>
+          <t>666019; 749273</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1006086; 1097432</t>
+          <t>1004199; 1101425</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>791261; 873248</t>
+          <t>787034; 873374</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>211633; 308238</t>
+          <t>204801; 307611</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1010970; 1103813</t>
+          <t>1015276; 1109391</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1499626; 1598359</t>
+          <t>1500332; 1600399</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1144915; 1243104</t>
+          <t>1143470; 1245192</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>424655; 1204557</t>
+          <t>425823; 1177672</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1698885; 1829024</t>
+          <t>1698777; 1830993</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2534906; 2676913</t>
+          <t>2536806; 2674204</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1958406; 2094518</t>
+          <t>1959385; 2091070</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>677673; 1551083</t>
+          <t>671468; 1555376</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,64; 23,91</t>
+          <t>17,52; 24,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,28; 31,3</t>
+          <t>24,26; 31,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,45; 31,54</t>
+          <t>23,44; 31,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 11,56</t>
+          <t>7,24; 11,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,79; 31,22</t>
+          <t>25,8; 31,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,04; 39,94</t>
+          <t>34,03; 39,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,05; 31,54</t>
+          <t>24,97; 31,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,27; 12,55</t>
+          <t>9,88; 13,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,25; 27,4</t>
+          <t>23,18; 27,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31,08; 35,75</t>
+          <t>31,1; 35,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,57; 30,76</t>
+          <t>25,26; 30,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,61; 11,4</t>
+          <t>9,18; 11,91</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,16; 48,8</t>
+          <t>42,14; 48,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55,27; 61,09</t>
+          <t>55,13; 61,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,74; 51,93</t>
+          <t>45,74; 52,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,3; 9,16</t>
+          <t>7,96; 10,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>56,22; 62,56</t>
+          <t>55,99; 62,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,99; 80,95</t>
+          <t>76,39; 81,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,94; 63,86</t>
+          <t>57,87; 63,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,5; 40,65</t>
+          <t>12,95; 15,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,6; 54,88</t>
+          <t>50,33; 54,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66,43; 70,4</t>
+          <t>66,42; 70,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53,04; 57,43</t>
+          <t>53,24; 57,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,64; 28,43</t>
+          <t>10,72; 12,72</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,72; 54,12</t>
+          <t>42,34; 54,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63,0; 75,05</t>
+          <t>62,43; 75,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50,05; 62,44</t>
+          <t>48,69; 62,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 9,83</t>
+          <t>5,39; 10,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54,35; 65,76</t>
+          <t>54,2; 66,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78,58; 88,82</t>
+          <t>79,18; 89,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,62; 76,29</t>
+          <t>65,48; 76,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,35; 12,22</t>
+          <t>8,65; 12,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50,04; 57,97</t>
+          <t>49,92; 58,17</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72,92; 80,86</t>
+          <t>72,89; 81,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60,21; 68,5</t>
+          <t>60,13; 68,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,13; 10,26</t>
+          <t>7,73; 10,8</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,87; 39,22</t>
+          <t>34,77; 39,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,04; 51,6</t>
+          <t>47,27; 51,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,67; 46,25</t>
+          <t>41,79; 46,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,93; 8,91</t>
+          <t>7,9; 10,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,12; 48,21</t>
+          <t>44,09; 48,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,69; 63,67</t>
+          <t>59,61; 63,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,06; 53,43</t>
+          <t>48,93; 53,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,65; 32,23</t>
+          <t>11,95; 13,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40,34; 43,48</t>
+          <t>40,25; 43,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54,57; 57,53</t>
+          <t>54,42; 57,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46,44; 49,56</t>
+          <t>46,58; 49,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,45; 21,89</t>
+          <t>10,2; 11,6</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46261</t>
+          <t>52771</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>80779</t>
+          <t>94762</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>127039</t>
+          <t>147533</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>119603; 162147</t>
+          <t>118817; 163824</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>174118; 224416</t>
+          <t>173915; 225440</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>121511; 163452</t>
+          <t>121452; 162208</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35711; 59525</t>
+          <t>41873; 68023</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>257945; 312237</t>
+          <t>257975; 313756</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>361559; 424244</t>
+          <t>361555; 424141</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>196765; 247788</t>
+          <t>196178; 248138</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>70035; 94845</t>
+          <t>81196; 111046</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>390126; 459794</t>
+          <t>389061; 459718</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>553089; 636153</t>
+          <t>553379; 636503</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>333325; 400996</t>
+          <t>329381; 397054</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>109436; 144843</t>
+          <t>128568; 166780</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>174242</t>
+          <t>206841</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>469960</t>
+          <t>307610</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>644202</t>
+          <t>514452</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>396364; 458834</t>
+          <t>396217; 459417</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>640079; 707484</t>
+          <t>638504; 707337</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>503990; 572281</t>
+          <t>504051; 573430</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>121446; 209820</t>
+          <t>177547; 235979</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>568428; 632516</t>
+          <t>566145; 629813</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>898844; 957522</t>
+          <t>903658; 959117</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>714198; 787049</t>
+          <t>713278; 783599</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>279658; 909568</t>
+          <t>281143; 343566</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>987361; 1070882</t>
+          <t>982049; 1068459</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1555089; 1648094</t>
+          <t>1554953; 1649826</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1238267; 1340667</t>
+          <t>1242933; 1337966</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>436733; 1287495</t>
+          <t>472106; 559858</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47013</t>
+          <t>53628</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>66435</t>
+          <t>78266</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>113448</t>
+          <t>131894</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>121774; 157984</t>
+          <t>123585; 157685</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>163540; 194812</t>
+          <t>162048; 196077</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>134299; 167537</t>
+          <t>130642; 166493</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33884; 63543</t>
+          <t>38365; 71410</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>157695; 190819</t>
+          <t>157269; 192927</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>211000; 238499</t>
+          <t>212620; 239088</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>205020; 238355</t>
+          <t>204584; 238364</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>55179; 80709</t>
+          <t>63565; 93929</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>291273; 337450</t>
+          <t>290596; 338577</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>385097; 427014</t>
+          <t>384946; 427891</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349653; 397831</t>
+          <t>349188; 397279</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>93172; 134055</t>
+          <t>111753; 156162</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>267516</t>
+          <t>313240</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>617174</t>
+          <t>480638</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>884690</t>
+          <t>793878</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>666019; 749273</t>
+          <t>664139; 750667</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1004199; 1101425</t>
+          <t>1009029; 1099527</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>787034; 873374</t>
+          <t>789286; 881874</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>204801; 307611</t>
+          <t>278291; 353270</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1015276; 1109391</t>
+          <t>1014719; 1108578</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1500332; 1600399</t>
+          <t>1498479; 1595453</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1143470; 1245192</t>
+          <t>1140340; 1240418</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>425823; 1177672</t>
+          <t>445487; 520734</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1698777; 1830993</t>
+          <t>1695103; 1826314</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2536806; 2674204</t>
+          <t>2529743; 2669451</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1959385; 2091070</t>
+          <t>1965320; 2094132</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>671468; 1555376</t>
+          <t>739045; 840926</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
